--- a/tests/fixtures/settled/j-and-m-woodworking.xlsx
+++ b/tests/fixtures/settled/j-and-m-woodworking.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Markup" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name=" Percentage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Hampton" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Specialty Finish Options" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Java" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Specialty Finish Options" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,7 +581,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nightstand with Fabric Panel</t>
+          <t>Nightstand</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -593,6 +594,89 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Java Collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Item #</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Br. Maple</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Side Chair Fabric</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Side Chair Crypton</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Side Chair Leather</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
